--- a/src/results.xlsx
+++ b/src/results.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G145"/>
+  <dimension ref="A1:G193"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3765,6 +3765,1110 @@
         <v>41.72</v>
       </c>
     </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>200</v>
+      </c>
+      <c r="B146" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C146" t="n">
+        <v>0</v>
+      </c>
+      <c r="D146" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E146" t="n">
+        <v>173.06</v>
+      </c>
+      <c r="F146" t="n">
+        <v>115.08</v>
+      </c>
+      <c r="G146" t="n">
+        <v>33.51</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>200</v>
+      </c>
+      <c r="B147" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C147" t="n">
+        <v>0</v>
+      </c>
+      <c r="D147" t="n">
+        <v>1</v>
+      </c>
+      <c r="E147" t="n">
+        <v>173.06</v>
+      </c>
+      <c r="F147" t="n">
+        <v>115.08</v>
+      </c>
+      <c r="G147" t="n">
+        <v>33.51</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>200</v>
+      </c>
+      <c r="B148" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C148" t="n">
+        <v>0</v>
+      </c>
+      <c r="D148" t="n">
+        <v>2</v>
+      </c>
+      <c r="E148" t="n">
+        <v>173.06</v>
+      </c>
+      <c r="F148" t="n">
+        <v>115.08</v>
+      </c>
+      <c r="G148" t="n">
+        <v>33.51</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>200</v>
+      </c>
+      <c r="B149" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C149" t="n">
+        <v>0</v>
+      </c>
+      <c r="D149" t="n">
+        <v>4</v>
+      </c>
+      <c r="E149" t="n">
+        <v>173.06</v>
+      </c>
+      <c r="F149" t="n">
+        <v>114.21</v>
+      </c>
+      <c r="G149" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>200</v>
+      </c>
+      <c r="B150" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C150" t="n">
+        <v>1</v>
+      </c>
+      <c r="D150" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E150" t="n">
+        <v>2869.09</v>
+      </c>
+      <c r="F150" t="n">
+        <v>2574.33</v>
+      </c>
+      <c r="G150" t="n">
+        <v>10.27</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>200</v>
+      </c>
+      <c r="B151" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C151" t="n">
+        <v>1</v>
+      </c>
+      <c r="D151" t="n">
+        <v>1</v>
+      </c>
+      <c r="E151" t="n">
+        <v>42318.66</v>
+      </c>
+      <c r="F151" t="n">
+        <v>42276.36</v>
+      </c>
+      <c r="G151" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>200</v>
+      </c>
+      <c r="B152" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C152" t="n">
+        <v>1</v>
+      </c>
+      <c r="D152" t="n">
+        <v>2</v>
+      </c>
+      <c r="E152" t="n">
+        <v>12839709.01</v>
+      </c>
+      <c r="F152" t="n">
+        <v>11732458.57</v>
+      </c>
+      <c r="G152" t="n">
+        <v>8.619999999999999</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>200</v>
+      </c>
+      <c r="B153" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C153" t="n">
+        <v>1</v>
+      </c>
+      <c r="D153" t="n">
+        <v>4</v>
+      </c>
+      <c r="E153" t="n">
+        <v>1818052590362.52</v>
+      </c>
+      <c r="F153" t="n">
+        <v>1272365277242.84</v>
+      </c>
+      <c r="G153" t="n">
+        <v>30.01</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>200</v>
+      </c>
+      <c r="B154" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C154" t="n">
+        <v>2</v>
+      </c>
+      <c r="D154" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E154" t="n">
+        <v>3985.82</v>
+      </c>
+      <c r="F154" t="n">
+        <v>3591.17</v>
+      </c>
+      <c r="G154" t="n">
+        <v>9.9</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>200</v>
+      </c>
+      <c r="B155" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C155" t="n">
+        <v>2</v>
+      </c>
+      <c r="D155" t="n">
+        <v>1</v>
+      </c>
+      <c r="E155" t="n">
+        <v>84464.25999999999</v>
+      </c>
+      <c r="F155" t="n">
+        <v>84422.73</v>
+      </c>
+      <c r="G155" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>200</v>
+      </c>
+      <c r="B156" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C156" t="n">
+        <v>2</v>
+      </c>
+      <c r="D156" t="n">
+        <v>2</v>
+      </c>
+      <c r="E156" t="n">
+        <v>51358316.85</v>
+      </c>
+      <c r="F156" t="n">
+        <v>46929374.12</v>
+      </c>
+      <c r="G156" t="n">
+        <v>8.619999999999999</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>200</v>
+      </c>
+      <c r="B157" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C157" t="n">
+        <v>2</v>
+      </c>
+      <c r="D157" t="n">
+        <v>4</v>
+      </c>
+      <c r="E157" t="n">
+        <v>29088841443204.32</v>
+      </c>
+      <c r="F157" t="n">
+        <v>20357844433638.15</v>
+      </c>
+      <c r="G157" t="n">
+        <v>30.01</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>200</v>
+      </c>
+      <c r="B158" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C158" t="n">
+        <v>4</v>
+      </c>
+      <c r="D158" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E158" t="n">
+        <v>5565.11</v>
+      </c>
+      <c r="F158" t="n">
+        <v>5029.08</v>
+      </c>
+      <c r="G158" t="n">
+        <v>9.630000000000001</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="n">
+        <v>200</v>
+      </c>
+      <c r="B159" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C159" t="n">
+        <v>4</v>
+      </c>
+      <c r="D159" t="n">
+        <v>1</v>
+      </c>
+      <c r="E159" t="n">
+        <v>168755.45</v>
+      </c>
+      <c r="F159" t="n">
+        <v>168714.63</v>
+      </c>
+      <c r="G159" t="n">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="n">
+        <v>200</v>
+      </c>
+      <c r="B160" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C160" t="n">
+        <v>4</v>
+      </c>
+      <c r="D160" t="n">
+        <v>2</v>
+      </c>
+      <c r="E160" t="n">
+        <v>205432748.2</v>
+      </c>
+      <c r="F160" t="n">
+        <v>187717036.34</v>
+      </c>
+      <c r="G160" t="n">
+        <v>8.619999999999999</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="n">
+        <v>200</v>
+      </c>
+      <c r="B161" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C161" t="n">
+        <v>4</v>
+      </c>
+      <c r="D161" t="n">
+        <v>4</v>
+      </c>
+      <c r="E161" t="n">
+        <v>465421463088673.1</v>
+      </c>
+      <c r="F161" t="n">
+        <v>325725510935964</v>
+      </c>
+      <c r="G161" t="n">
+        <v>30.01</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="n">
+        <v>200</v>
+      </c>
+      <c r="B162" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C162" t="n">
+        <v>0</v>
+      </c>
+      <c r="D162" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E162" t="n">
+        <v>152.98</v>
+      </c>
+      <c r="F162" t="n">
+        <v>96.89</v>
+      </c>
+      <c r="G162" t="n">
+        <v>36.67</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="n">
+        <v>200</v>
+      </c>
+      <c r="B163" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C163" t="n">
+        <v>0</v>
+      </c>
+      <c r="D163" t="n">
+        <v>1</v>
+      </c>
+      <c r="E163" t="n">
+        <v>152.98</v>
+      </c>
+      <c r="F163" t="n">
+        <v>96.89</v>
+      </c>
+      <c r="G163" t="n">
+        <v>36.67</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="n">
+        <v>200</v>
+      </c>
+      <c r="B164" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C164" t="n">
+        <v>0</v>
+      </c>
+      <c r="D164" t="n">
+        <v>2</v>
+      </c>
+      <c r="E164" t="n">
+        <v>152.98</v>
+      </c>
+      <c r="F164" t="n">
+        <v>96.89</v>
+      </c>
+      <c r="G164" t="n">
+        <v>36.67</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="n">
+        <v>200</v>
+      </c>
+      <c r="B165" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C165" t="n">
+        <v>0</v>
+      </c>
+      <c r="D165" t="n">
+        <v>4</v>
+      </c>
+      <c r="E165" t="n">
+        <v>152.98</v>
+      </c>
+      <c r="F165" t="n">
+        <v>95.62</v>
+      </c>
+      <c r="G165" t="n">
+        <v>37.49</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="n">
+        <v>200</v>
+      </c>
+      <c r="B166" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C166" t="n">
+        <v>1</v>
+      </c>
+      <c r="D166" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E166" t="n">
+        <v>2670.56</v>
+      </c>
+      <c r="F166" t="n">
+        <v>2334.8</v>
+      </c>
+      <c r="G166" t="n">
+        <v>12.57</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="n">
+        <v>200</v>
+      </c>
+      <c r="B167" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C167" t="n">
+        <v>1</v>
+      </c>
+      <c r="D167" t="n">
+        <v>1</v>
+      </c>
+      <c r="E167" t="n">
+        <v>37330.08</v>
+      </c>
+      <c r="F167" t="n">
+        <v>37295.1</v>
+      </c>
+      <c r="G167" t="n">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="n">
+        <v>200</v>
+      </c>
+      <c r="B168" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C168" t="n">
+        <v>1</v>
+      </c>
+      <c r="D168" t="n">
+        <v>2</v>
+      </c>
+      <c r="E168" t="n">
+        <v>10258039.46</v>
+      </c>
+      <c r="F168" t="n">
+        <v>9330073.4</v>
+      </c>
+      <c r="G168" t="n">
+        <v>9.050000000000001</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="n">
+        <v>200</v>
+      </c>
+      <c r="B169" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C169" t="n">
+        <v>1</v>
+      </c>
+      <c r="D169" t="n">
+        <v>4</v>
+      </c>
+      <c r="E169" t="n">
+        <v>1222098394194.95</v>
+      </c>
+      <c r="F169" t="n">
+        <v>854957688574.33</v>
+      </c>
+      <c r="G169" t="n">
+        <v>30.04</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="n">
+        <v>200</v>
+      </c>
+      <c r="B170" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C170" t="n">
+        <v>2</v>
+      </c>
+      <c r="D170" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E170" t="n">
+        <v>3713.38</v>
+      </c>
+      <c r="F170" t="n">
+        <v>3259.64</v>
+      </c>
+      <c r="G170" t="n">
+        <v>12.22</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="n">
+        <v>200</v>
+      </c>
+      <c r="B171" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C171" t="n">
+        <v>2</v>
+      </c>
+      <c r="D171" t="n">
+        <v>1</v>
+      </c>
+      <c r="E171" t="n">
+        <v>74507.17999999999</v>
+      </c>
+      <c r="F171" t="n">
+        <v>74476.98</v>
+      </c>
+      <c r="G171" t="n">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="n">
+        <v>200</v>
+      </c>
+      <c r="B172" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C172" t="n">
+        <v>2</v>
+      </c>
+      <c r="D172" t="n">
+        <v>2</v>
+      </c>
+      <c r="E172" t="n">
+        <v>41031698.91</v>
+      </c>
+      <c r="F172" t="n">
+        <v>37319891.87</v>
+      </c>
+      <c r="G172" t="n">
+        <v>9.050000000000001</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="n">
+        <v>200</v>
+      </c>
+      <c r="B173" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C173" t="n">
+        <v>2</v>
+      </c>
+      <c r="D173" t="n">
+        <v>4</v>
+      </c>
+      <c r="E173" t="n">
+        <v>19553574304824.58</v>
+      </c>
+      <c r="F173" t="n">
+        <v>13679323015235.86</v>
+      </c>
+      <c r="G173" t="n">
+        <v>30.04</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="n">
+        <v>200</v>
+      </c>
+      <c r="B174" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C174" t="n">
+        <v>4</v>
+      </c>
+      <c r="D174" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E174" t="n">
+        <v>5188.14</v>
+      </c>
+      <c r="F174" t="n">
+        <v>4567.52</v>
+      </c>
+      <c r="G174" t="n">
+        <v>11.96</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="n">
+        <v>200</v>
+      </c>
+      <c r="B175" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C175" t="n">
+        <v>4</v>
+      </c>
+      <c r="D175" t="n">
+        <v>1</v>
+      </c>
+      <c r="E175" t="n">
+        <v>148861.37</v>
+      </c>
+      <c r="F175" t="n">
+        <v>148834.12</v>
+      </c>
+      <c r="G175" t="n">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="n">
+        <v>200</v>
+      </c>
+      <c r="B176" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C176" t="n">
+        <v>4</v>
+      </c>
+      <c r="D176" t="n">
+        <v>2</v>
+      </c>
+      <c r="E176" t="n">
+        <v>164126336.7</v>
+      </c>
+      <c r="F176" t="n">
+        <v>149279165.74</v>
+      </c>
+      <c r="G176" t="n">
+        <v>9.050000000000001</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="n">
+        <v>200</v>
+      </c>
+      <c r="B177" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C177" t="n">
+        <v>4</v>
+      </c>
+      <c r="D177" t="n">
+        <v>4</v>
+      </c>
+      <c r="E177" t="n">
+        <v>312857188874898.4</v>
+      </c>
+      <c r="F177" t="n">
+        <v>218869168241820.6</v>
+      </c>
+      <c r="G177" t="n">
+        <v>30.04</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="n">
+        <v>200</v>
+      </c>
+      <c r="B178" t="n">
+        <v>1</v>
+      </c>
+      <c r="C178" t="n">
+        <v>0</v>
+      </c>
+      <c r="D178" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E178" t="n">
+        <v>150.57</v>
+      </c>
+      <c r="F178" t="n">
+        <v>93.2</v>
+      </c>
+      <c r="G178" t="n">
+        <v>38.1</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="n">
+        <v>200</v>
+      </c>
+      <c r="B179" t="n">
+        <v>1</v>
+      </c>
+      <c r="C179" t="n">
+        <v>0</v>
+      </c>
+      <c r="D179" t="n">
+        <v>1</v>
+      </c>
+      <c r="E179" t="n">
+        <v>150.57</v>
+      </c>
+      <c r="F179" t="n">
+        <v>93.2</v>
+      </c>
+      <c r="G179" t="n">
+        <v>38.1</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="n">
+        <v>200</v>
+      </c>
+      <c r="B180" t="n">
+        <v>1</v>
+      </c>
+      <c r="C180" t="n">
+        <v>0</v>
+      </c>
+      <c r="D180" t="n">
+        <v>2</v>
+      </c>
+      <c r="E180" t="n">
+        <v>150.57</v>
+      </c>
+      <c r="F180" t="n">
+        <v>93.2</v>
+      </c>
+      <c r="G180" t="n">
+        <v>38.1</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="n">
+        <v>200</v>
+      </c>
+      <c r="B181" t="n">
+        <v>1</v>
+      </c>
+      <c r="C181" t="n">
+        <v>0</v>
+      </c>
+      <c r="D181" t="n">
+        <v>4</v>
+      </c>
+      <c r="E181" t="n">
+        <v>150.57</v>
+      </c>
+      <c r="F181" t="n">
+        <v>92.11</v>
+      </c>
+      <c r="G181" t="n">
+        <v>38.82</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="n">
+        <v>200</v>
+      </c>
+      <c r="B182" t="n">
+        <v>1</v>
+      </c>
+      <c r="C182" t="n">
+        <v>1</v>
+      </c>
+      <c r="D182" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E182" t="n">
+        <v>2632.67</v>
+      </c>
+      <c r="F182" t="n">
+        <v>2259.44</v>
+      </c>
+      <c r="G182" t="n">
+        <v>14.18</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="n">
+        <v>200</v>
+      </c>
+      <c r="B183" t="n">
+        <v>1</v>
+      </c>
+      <c r="C183" t="n">
+        <v>1</v>
+      </c>
+      <c r="D183" t="n">
+        <v>1</v>
+      </c>
+      <c r="E183" t="n">
+        <v>36502.65</v>
+      </c>
+      <c r="F183" t="n">
+        <v>36466.7</v>
+      </c>
+      <c r="G183" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="n">
+        <v>200</v>
+      </c>
+      <c r="B184" t="n">
+        <v>1</v>
+      </c>
+      <c r="C184" t="n">
+        <v>1</v>
+      </c>
+      <c r="D184" t="n">
+        <v>2</v>
+      </c>
+      <c r="E184" t="n">
+        <v>9987325.619999999</v>
+      </c>
+      <c r="F184" t="n">
+        <v>9363779.460000001</v>
+      </c>
+      <c r="G184" t="n">
+        <v>6.24</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="n">
+        <v>200</v>
+      </c>
+      <c r="B185" t="n">
+        <v>1</v>
+      </c>
+      <c r="C185" t="n">
+        <v>1</v>
+      </c>
+      <c r="D185" t="n">
+        <v>4</v>
+      </c>
+      <c r="E185" t="n">
+        <v>1194412562104.29</v>
+      </c>
+      <c r="F185" t="n">
+        <v>955754251550.87</v>
+      </c>
+      <c r="G185" t="n">
+        <v>19.98</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="n">
+        <v>200</v>
+      </c>
+      <c r="B186" t="n">
+        <v>1</v>
+      </c>
+      <c r="C186" t="n">
+        <v>2</v>
+      </c>
+      <c r="D186" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E186" t="n">
+        <v>3660.78</v>
+      </c>
+      <c r="F186" t="n">
+        <v>3154.67</v>
+      </c>
+      <c r="G186" t="n">
+        <v>13.83</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="n">
+        <v>200</v>
+      </c>
+      <c r="B187" t="n">
+        <v>1</v>
+      </c>
+      <c r="C187" t="n">
+        <v>2</v>
+      </c>
+      <c r="D187" t="n">
+        <v>1</v>
+      </c>
+      <c r="E187" t="n">
+        <v>72854.73</v>
+      </c>
+      <c r="F187" t="n">
+        <v>72825.58</v>
+      </c>
+      <c r="G187" t="n">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="n">
+        <v>200</v>
+      </c>
+      <c r="B188" t="n">
+        <v>1</v>
+      </c>
+      <c r="C188" t="n">
+        <v>2</v>
+      </c>
+      <c r="D188" t="n">
+        <v>2</v>
+      </c>
+      <c r="E188" t="n">
+        <v>39948850.77</v>
+      </c>
+      <c r="F188" t="n">
+        <v>37454722.79</v>
+      </c>
+      <c r="G188" t="n">
+        <v>6.24</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="n">
+        <v>200</v>
+      </c>
+      <c r="B189" t="n">
+        <v>1</v>
+      </c>
+      <c r="C189" t="n">
+        <v>2</v>
+      </c>
+      <c r="D189" t="n">
+        <v>4</v>
+      </c>
+      <c r="E189" t="n">
+        <v>19110600991410.08</v>
+      </c>
+      <c r="F189" t="n">
+        <v>15292068022883.26</v>
+      </c>
+      <c r="G189" t="n">
+        <v>19.98</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="n">
+        <v>200</v>
+      </c>
+      <c r="B190" t="n">
+        <v>1</v>
+      </c>
+      <c r="C190" t="n">
+        <v>4</v>
+      </c>
+      <c r="D190" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E190" t="n">
+        <v>5114.76</v>
+      </c>
+      <c r="F190" t="n">
+        <v>4420.72</v>
+      </c>
+      <c r="G190" t="n">
+        <v>13.57</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="n">
+        <v>200</v>
+      </c>
+      <c r="B191" t="n">
+        <v>1</v>
+      </c>
+      <c r="C191" t="n">
+        <v>4</v>
+      </c>
+      <c r="D191" t="n">
+        <v>1</v>
+      </c>
+      <c r="E191" t="n">
+        <v>145558.89</v>
+      </c>
+      <c r="F191" t="n">
+        <v>145535.29</v>
+      </c>
+      <c r="G191" t="n">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="n">
+        <v>200</v>
+      </c>
+      <c r="B192" t="n">
+        <v>1</v>
+      </c>
+      <c r="C192" t="n">
+        <v>4</v>
+      </c>
+      <c r="D192" t="n">
+        <v>2</v>
+      </c>
+      <c r="E192" t="n">
+        <v>159794951.37</v>
+      </c>
+      <c r="F192" t="n">
+        <v>149818496.12</v>
+      </c>
+      <c r="G192" t="n">
+        <v>6.24</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="n">
+        <v>200</v>
+      </c>
+      <c r="B193" t="n">
+        <v>1</v>
+      </c>
+      <c r="C193" t="n">
+        <v>4</v>
+      </c>
+      <c r="D193" t="n">
+        <v>4</v>
+      </c>
+      <c r="E193" t="n">
+        <v>305769615860302.6</v>
+      </c>
+      <c r="F193" t="n">
+        <v>244673088364201.4</v>
+      </c>
+      <c r="G193" t="n">
+        <v>19.98</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
